--- a/Config/GuideGroupConfig.xlsx
+++ b/Config/GuideGroupConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,6 +552,31 @@
         </is>
       </c>
       <c r="G4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FirstTalentDraw</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>true</t>
         </is>

--- a/Config/GuideGroupConfig.xlsx
+++ b/Config/GuideGroupConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,6 +582,86 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FirstShop</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ScreenOpen</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>App.BattleShopPop</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FirstSkill</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>FirstBond</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
